--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,694 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131934198</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57210</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Kvarnbacken, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587459</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6357699</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131934256</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Venerna, Venerna, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>587510</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6357635</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131933260</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>587452</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6357809</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131933097</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57918</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>587452</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6357809</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131932229</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79886</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>587489</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6357780</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131933189</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58062</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>587452</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6357809</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>131934198</v>
       </c>
       <c r="B5" t="n">
-        <v>57210</v>
+        <v>57212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131934256</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131933260</v>
+        <v>131933097</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,14 +1280,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1368,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131933097</v>
+        <v>131933260</v>
       </c>
       <c r="B8" t="n">
-        <v>57918</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,16 +1375,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,10 +1392,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1483,7 +1483,7 @@
         <v>131932229</v>
       </c>
       <c r="B9" t="n">
-        <v>79886</v>
+        <v>79888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>131933189</v>
       </c>
       <c r="B10" t="n">
-        <v>58062</v>
+        <v>58064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>131934198</v>
       </c>
       <c r="B5" t="n">
-        <v>57212</v>
+        <v>57217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131934256</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131933097</v>
+        <v>131933260</v>
       </c>
       <c r="B7" t="n">
-        <v>57920</v>
+        <v>57909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,10 +1280,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1364,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131933260</v>
+        <v>131933097</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,16 +1379,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1392,14 +1396,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1483,7 +1483,7 @@
         <v>131932229</v>
       </c>
       <c r="B9" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>131933189</v>
       </c>
       <c r="B10" t="n">
-        <v>58064</v>
+        <v>58069</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,7 +1018,7 @@
         <v>131934198</v>
       </c>
       <c r="B5" t="n">
-        <v>57217</v>
+        <v>57219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131934256</v>
       </c>
       <c r="B6" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131933260</v>
       </c>
       <c r="B7" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>131933097</v>
       </c>
       <c r="B8" t="n">
-        <v>57925</v>
+        <v>57927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131932229</v>
       </c>
       <c r="B9" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>131933189</v>
       </c>
       <c r="B10" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,6 +1700,712 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132168843</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5029</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101608</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asppraktbagge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecilonota variolosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Paykull, 1799)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>587470</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6357684</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132168844</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96362</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>587340</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6357786</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132168846</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58071</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>587391</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6357721</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132168847</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91806</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>587433</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6357840</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132168845</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96362</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>587514</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6357704</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132168842</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57911</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>587458</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6357765</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132168840</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5364</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>587470</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6357684</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131933260</v>
+        <v>131933097</v>
       </c>
       <c r="B7" t="n">
-        <v>57911</v>
+        <v>57927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,14 +1280,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1368,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131933097</v>
+        <v>131933260</v>
       </c>
       <c r="B8" t="n">
-        <v>57927</v>
+        <v>57911</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,16 +1375,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,10 +1392,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131933097</v>
+        <v>131933260</v>
       </c>
       <c r="B7" t="n">
-        <v>57927</v>
+        <v>57911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,10 +1280,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1364,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131933260</v>
+        <v>131933097</v>
       </c>
       <c r="B8" t="n">
-        <v>57911</v>
+        <v>57927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,16 +1379,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1392,14 +1396,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>131934198</v>
       </c>
       <c r="B5" t="n">
-        <v>57219</v>
+        <v>57253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131934256</v>
       </c>
       <c r="B6" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131933260</v>
+        <v>131933097</v>
       </c>
       <c r="B7" t="n">
-        <v>57911</v>
+        <v>57961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,14 +1280,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1368,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131933097</v>
+        <v>131933260</v>
       </c>
       <c r="B8" t="n">
-        <v>57927</v>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,16 +1375,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,10 +1392,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1483,7 +1483,7 @@
         <v>131932229</v>
       </c>
       <c r="B9" t="n">
-        <v>79895</v>
+        <v>79929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>131933189</v>
       </c>
       <c r="B10" t="n">
-        <v>58071</v>
+        <v>58105</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>132168844</v>
       </c>
       <c r="B12" t="n">
-        <v>96362</v>
+        <v>96398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>132168846</v>
       </c>
       <c r="B13" t="n">
-        <v>58071</v>
+        <v>58105</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132168847</v>
       </c>
       <c r="B14" t="n">
-        <v>91806</v>
+        <v>91842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>132168845</v>
       </c>
       <c r="B15" t="n">
-        <v>96362</v>
+        <v>96398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>132168842</v>
       </c>
       <c r="B16" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131933260</v>
+        <v>131933097</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>57961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,14 +1280,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1368,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131933097</v>
+        <v>131933260</v>
       </c>
       <c r="B8" t="n">
-        <v>57961</v>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,16 +1375,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,10 +1392,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1483,7 +1483,7 @@
         <v>131932229</v>
       </c>
       <c r="B9" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>131933189</v>
       </c>
       <c r="B10" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>132168844</v>
       </c>
       <c r="B12" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>132168846</v>
       </c>
       <c r="B13" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132168847</v>
       </c>
       <c r="B14" t="n">
-        <v>91847</v>
+        <v>91850</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>132168845</v>
       </c>
       <c r="B15" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>131934198</v>
       </c>
       <c r="B5" t="n">
-        <v>57253</v>
+        <v>57254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131934256</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>131933097</v>
       </c>
       <c r="B7" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>131933260</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131932229</v>
       </c>
       <c r="B9" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>131933189</v>
       </c>
       <c r="B10" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>132168844</v>
       </c>
       <c r="B12" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>132168846</v>
       </c>
       <c r="B13" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132168847</v>
       </c>
       <c r="B14" t="n">
-        <v>91850</v>
+        <v>91856</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>132168845</v>
       </c>
       <c r="B15" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>132168842</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>131934198</v>
       </c>
       <c r="B5" t="n">
-        <v>57254</v>
+        <v>57258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131934256</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131933097</v>
+        <v>131933260</v>
       </c>
       <c r="B7" t="n">
-        <v>57962</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,10 +1280,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1364,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131933260</v>
+        <v>131933097</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>57966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,16 +1379,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1392,14 +1396,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1483,7 +1483,7 @@
         <v>131932229</v>
       </c>
       <c r="B9" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>131933189</v>
       </c>
       <c r="B10" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>132168844</v>
       </c>
       <c r="B12" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>132168846</v>
       </c>
       <c r="B13" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132168847</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>91866</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>132168845</v>
       </c>
       <c r="B15" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>132168842</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>132168844</v>
       </c>
       <c r="B12" t="n">
-        <v>96424</v>
+        <v>96426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132168847</v>
       </c>
       <c r="B14" t="n">
-        <v>91866</v>
+        <v>91867</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>132168845</v>
       </c>
       <c r="B15" t="n">
-        <v>96424</v>
+        <v>96426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>132168844</v>
       </c>
       <c r="B12" t="n">
-        <v>96426</v>
+        <v>96427</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>132168846</v>
       </c>
       <c r="B13" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132168847</v>
       </c>
       <c r="B14" t="n">
-        <v>91867</v>
+        <v>91868</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>132168845</v>
       </c>
       <c r="B15" t="n">
-        <v>96426</v>
+        <v>96427</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>132168842</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>132168844</v>
       </c>
       <c r="B12" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132168847</v>
       </c>
       <c r="B14" t="n">
-        <v>91868</v>
+        <v>91870</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>132168845</v>
       </c>
       <c r="B15" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>132168844</v>
       </c>
       <c r="B12" t="n">
-        <v>96429</v>
+        <v>96430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>132168847</v>
       </c>
       <c r="B14" t="n">
-        <v>91870</v>
+        <v>91871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>132168845</v>
       </c>
       <c r="B15" t="n">
-        <v>96429</v>
+        <v>96430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16752639</v>
+        <v>131932519</v>
       </c>
       <c r="B2" t="n">
-        <v>90596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Virån 44, Sm</t>
+          <t>Kvarnbacken, Kvarnbacken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587451.2519601076</v>
+        <v>587427</v>
       </c>
       <c r="R2" t="n">
-        <v>6357753.691610677</v>
+        <v>6357798</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,34 +764,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16752640</v>
+        <v>132168844</v>
       </c>
       <c r="B3" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,39 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Virån 44, Sm</t>
+          <t>Ängelsgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587451.2519601076</v>
+        <v>587340</v>
       </c>
       <c r="R3" t="n">
-        <v>6357753.691610677</v>
+        <v>6357786</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-07-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74430017</v>
+        <v>132168845</v>
       </c>
       <c r="B4" t="n">
-        <v>105817</v>
+        <v>96501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängelsgöl, syd, Sm</t>
+          <t>Ängelsgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587381</v>
+        <v>587514</v>
       </c>
       <c r="R4" t="n">
-        <v>6357686</v>
+        <v>6357704</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,17 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2005-09-03</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2005-09-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6G1h 3839. SOM: Galium odoratum. LEG: Åke Rühling</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,84 +960,61 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131934198</v>
+        <v>132168847</v>
       </c>
       <c r="B5" t="n">
-        <v>57258</v>
+        <v>91932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100065</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Kvarnbacken, Sm</t>
+          <t>Ängelsgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587459</v>
+        <v>587433</v>
       </c>
       <c r="R5" t="n">
-        <v>6357699</v>
+        <v>6357840</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,19 +1044,9 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131934256</v>
+        <v>131932229</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>79992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,43 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Venerna, Venerna, Sm</t>
+          <t>Ängelsgöl, Ängelsgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587510</v>
+        <v>587489</v>
       </c>
       <c r="R6" t="n">
-        <v>6357635</v>
+        <v>6357780</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,7 +1143,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1153,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131933260</v>
+        <v>131933097</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1191,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1280,14 +1208,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1368,27 +1292,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131933097</v>
+        <v>131933260</v>
       </c>
       <c r="B8" t="n">
-        <v>57966</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,10 +1320,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1480,45 +1408,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131932229</v>
+        <v>131934256</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ängelsgöl, Ängelsgöl, Sm</t>
+          <t>Venerna, Venerna, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587489</v>
+        <v>587510</v>
       </c>
       <c r="R9" t="n">
-        <v>6357780</v>
+        <v>6357635</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,7 +1487,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1497,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,27 +1524,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131933189</v>
+        <v>132168842</v>
       </c>
       <c r="B10" t="n">
-        <v>58112</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1615,26 +1552,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ängelsgöl, Ängelsgöl, Sm</t>
+          <t>Ängelsgöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587452</v>
+        <v>587458</v>
       </c>
       <c r="R10" t="n">
-        <v>6357809</v>
+        <v>6357765</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1664,19 +1592,14 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:10</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,62 +1614,71 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132168843</v>
+        <v>131934198</v>
       </c>
       <c r="B11" t="n">
-        <v>5029</v>
+        <v>57280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101608</v>
+        <v>100065</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ängelsgöl, Sm</t>
+          <t>Kvarnbacken, Kvarnbacken, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587470</v>
+        <v>587459</v>
       </c>
       <c r="R11" t="n">
-        <v>6357684</v>
+        <v>6357699</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1776,14 +1708,19 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,29 +1729,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132168844</v>
+        <v>131932839</v>
       </c>
       <c r="B12" t="n">
-        <v>96430</v>
+        <v>56783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,34 +1758,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2671</v>
+        <v>100077</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ängelsgöl, Sm</t>
+          <t>Kvarnbacken, Kvarnbacken, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587340</v>
+        <v>587427</v>
       </c>
       <c r="R12" t="n">
-        <v>6357786</v>
+        <v>6357798</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,9 +1820,19 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,60 +1847,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132168846</v>
+        <v>131786149</v>
       </c>
       <c r="B13" t="n">
-        <v>58113</v>
+        <v>44182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>101735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ängelsgöl, Sm</t>
+          <t>Kvarnbacken, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587391</v>
+        <v>587415</v>
       </c>
       <c r="R13" t="n">
-        <v>6357721</v>
+        <v>6357796</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,12 +1924,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,44 +1944,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132168847</v>
+        <v>132168841</v>
       </c>
       <c r="B14" t="n">
-        <v>91871</v>
+        <v>58250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5445</v>
+        <v>103019</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587433</v>
+        <v>587447</v>
       </c>
       <c r="R14" t="n">
-        <v>6357840</v>
+        <v>6357767</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2102,45 +2053,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132168845</v>
+        <v>131931873</v>
       </c>
       <c r="B15" t="n">
-        <v>96430</v>
+        <v>58134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2671</v>
+        <v>103020</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ängelsgöl, Sm</t>
+          <t>Ängelsgöl, Ängelsgöl, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587514</v>
+        <v>587507</v>
       </c>
       <c r="R15" t="n">
-        <v>6357704</v>
+        <v>6357713</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2170,9 +2130,19 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,22 +2157,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132168842</v>
+        <v>131933189</v>
       </c>
       <c r="B16" t="n">
-        <v>57951</v>
+        <v>58134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,16 +2180,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2227,17 +2197,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ängelsgöl, Sm</t>
+          <t>Ängelsgöl, Ängelsgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587458</v>
+        <v>587452</v>
       </c>
       <c r="R16" t="n">
-        <v>6357765</v>
+        <v>6357809</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2267,14 +2246,19 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,22 +2273,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132168840</v>
+        <v>132168846</v>
       </c>
       <c r="B17" t="n">
-        <v>5364</v>
+        <v>58134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2312,39 +2296,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101728</v>
+        <v>103020</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ängelsgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587470</v>
+        <v>587391</v>
       </c>
       <c r="R17" t="n">
-        <v>6357684</v>
+        <v>6357721</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2379,18 +2358,12 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2406,6 +2379,117 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>74430017</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ängelsgöl, syd, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>587381</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6357686</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2005-09-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2005-09-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G1h 3839. SOM: Galium odoratum. LEG: Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8258-2026 artfynd.xlsx
+++ b/artfynd/A 8258-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932519</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132168844</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132168845</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132168847</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932229</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933097</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933260</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934256</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132168842</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1744,6 +1794,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131934198</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1856,6 +1911,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131932839</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,6 +2013,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131786149</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132168841</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131931873</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131933189</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132168846</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2490,8 +2575,32 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74430017</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>